--- a/weekly_update/budget management web.xlsx
+++ b/weekly_update/budget management web.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Create backend/ + frontend/ folder structure per architecture plan</t>
+          <t>Master table editors use SWA + Functions + Vanilla JS. Main budget app (submit/approve/dashboard) will use FastAPI + React — more complex state and workflow</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>13-May-26</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>main.py + routers: /api/auth, /api/budget, /api/approval, /api/dashboard, /api/admin</t>
+          <t>For main budget app: /api/auth, /api/budget, /api/approval, /api/dashboard, /api/admin</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>13-May-26</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Pages: Login, Submit Budget (Template 1.1), Approve (VP/Staff/Manager), Dashboard, Admin</t>
+          <t>For main budget app: Login, Submit Budget (Template 1.1), Approve (VP/Staff/Manager), Dashboard, Admin</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>13-May-26</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Add 4 cols to sap_t_gl_trans: Entry Date, Order, Object Class, Order Short Text. Ratima สร้าง SAP_T_GL_TRANS_1000_RATIMA_TEST1 เสร็จแล้ว — กำลังตรวจสอบข้อมูลในไฟล์</t>
+          <t>4 cols added to sap_t_gl_trans: Entry Date, Order, Object Class, Order Short Text. Ratima verified data in SAP_T_GL_TRANS_1000_RATIMA_TEST1 ✅</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>13-May-26</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Verify no data loss after transform: null counts per col, row counts match, date cols parse correctly, amount sign-flip correct</t>
+          <t>Verified: sap_m_gl_account row count match, non-null counts match, distinct counts match, date cols parse correctly ✅</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>08-May-26</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Need API: orgcode → cost_center mapping. API structure to request: empcode, primary_orgcode, primary_costcenter, all_positions[]</t>
+          <t>orgcode → cost_center mapping received. Source: docs/09orgcode &amp; costcenter.xlsx (729 rows, 183 orgcodes, 205 CCs) — many-to-many confirmed</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
@@ -1819,6 +1819,105 @@
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>0003-gl-group Master Table Editor</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>GL Group CRUD on Azure SWA — GL codes from Fabric Lakehouse gold_sap_m_gl_account_group_name (430 SAP codes), sort/filter/export CSV, event delegation CSP compliance, thread-local DB connections. Deployed + tested ✅</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Jakkarit</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Data Pipeline</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>silver_sap_m_gl_account (GL Account Master)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>bronze_sap_m_gl_account → silver via sc() helper, ERDAT cast with to_date(c,'yyyyMMdd'), consistency check done</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Jakkarit</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Data Pipeline</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>gold_sap_m_gl_account_group_name</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>gold_sap_m_gl_account (filter chart_of_accounts=1000, starts 5/6, distinct) → left join gl_group_mapping + gl_group_dim → 430 rows (137 matched, 293 unmatched SAP codes)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Jakkarit</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>26-May-26</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_update/budget management web.xlsx
+++ b/weekly_update/budget management web.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1919,6 +1919,72 @@
       </c>
       <c r="G41" s="11" t="inlineStr"/>
     </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Project Action</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Approval Workflow — Finalize User &amp; Role Analysis</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>273 users confirmed: 177 submitter, 73 submitter+approver1, 21 approver1_only, Nipaporn+Waraporn dual-role. managerempcode-based chain. Special cases all confirmed. budget_actors_full.csv generated (16 cols).</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Jakkarit</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>27-May-26</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Project Action</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Approval Workflow Spec — Draft (needs review)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>requirement_spec/3_approval_workflow/approval_workflow_spec.md + .pdf created — chain, special cases, C-Level map, status flow, email triggers, signature block. INCOMPLETE — needs review and sign-off.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Jakkarit</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>28-May-26</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
